--- a/가계부_샘플.xlsx
+++ b/가계부_샘플.xlsx
@@ -1,46 +1,231 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skstk\Desktop\next-project\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91261B8D-3333-45BC-ADD2-0BE7652CE9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="3523" yWindow="3969" windowWidth="18514" windowHeight="10740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="60">
+  <si>
+    <t>일자</t>
+  </si>
+  <si>
+    <t>분류</t>
+  </si>
+  <si>
+    <t>카테고리</t>
+  </si>
+  <si>
+    <t>금액</t>
+  </si>
+  <si>
+    <t>내용</t>
+  </si>
+  <si>
+    <t>결제수단</t>
+  </si>
+  <si>
+    <t>주체</t>
+  </si>
+  <si>
+    <t>남편</t>
+  </si>
+  <si>
+    <t>지출</t>
+  </si>
+  <si>
+    <t>신용카드</t>
+  </si>
+  <si>
+    <t>교육</t>
+  </si>
+  <si>
+    <t>생활편의</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)이니시스 - 넥스트러너스 주식회사</t>
+  </si>
+  <si>
+    <t>의료/건강</t>
+  </si>
+  <si>
+    <t>일산21세기병원</t>
+  </si>
+  <si>
+    <t>마트/편의점</t>
+  </si>
+  <si>
+    <t>이마트에브리데이은평수색점</t>
+  </si>
+  <si>
+    <t>경희이루리한의원</t>
+  </si>
+  <si>
+    <t>외식</t>
+  </si>
+  <si>
+    <t>파리바게뜨수색점</t>
+  </si>
+  <si>
+    <t>기타</t>
+  </si>
+  <si>
+    <t>토스페이먼츠 - 구글클라우드</t>
+  </si>
+  <si>
+    <t>잉치킨수색아이파크점</t>
+  </si>
+  <si>
+    <t>우정사업본부우체국</t>
+  </si>
+  <si>
+    <t>향동365정형외과의원</t>
+  </si>
+  <si>
+    <t>쿨마트</t>
+  </si>
+  <si>
+    <t>향동온누리약국</t>
+  </si>
+  <si>
+    <t>씨유CU킨텍스3호점</t>
+  </si>
+  <si>
+    <t>교통</t>
+  </si>
+  <si>
+    <t>KCP - 아이파킹 주식회사</t>
+  </si>
+  <si>
+    <t>뚱땡이김밥</t>
+  </si>
+  <si>
+    <t>주유</t>
+  </si>
+  <si>
+    <t>소담촌수색상암DMC점</t>
+  </si>
+  <si>
+    <t>KCP - 쿠팡</t>
+  </si>
+  <si>
+    <t>코레일유통용산역</t>
+  </si>
+  <si>
+    <t>쇼핑/미용</t>
+  </si>
+  <si>
+    <t>에이치디씨아이파크몰</t>
+  </si>
+  <si>
+    <t>샐활편의</t>
+  </si>
+  <si>
+    <t>네이버페이</t>
+  </si>
+  <si>
+    <t>나이스 - 쿠팡</t>
+  </si>
+  <si>
+    <t>통신</t>
+  </si>
+  <si>
+    <t>휴대폰</t>
+  </si>
+  <si>
+    <t>한국정보통신 - 쿠팡</t>
+  </si>
+  <si>
+    <t>G마켓</t>
+  </si>
+  <si>
+    <t>홍익보조기</t>
+  </si>
+  <si>
+    <t>보험</t>
+  </si>
+  <si>
+    <t>한화손해보험</t>
+  </si>
+  <si>
+    <t>컴포즈커피행주산성점</t>
+  </si>
+  <si>
+    <t>원조집</t>
+  </si>
+  <si>
+    <t>02월모바일티머니버스 0003건</t>
+  </si>
+  <si>
+    <t>02월티머니지하철 0001건</t>
+  </si>
+  <si>
+    <t>02월경기마을 0001건</t>
+  </si>
+  <si>
+    <t>02월티머니버스 0001건</t>
+  </si>
+  <si>
+    <t>02월경기시내버스 0001건</t>
+  </si>
+  <si>
+    <t>02월모바일티머니지하철 0005건</t>
+  </si>
+  <si>
+    <t>문화/여가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구독_CapCut,KRW:11900.00 </t>
+  </si>
+  <si>
+    <t>구독_Shopee - Singapore,SGD:10.00</t>
+  </si>
+  <si>
+    <t>나이스 - 쿠팡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -64,14 +249,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,265 +590,1221 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="16.3984375" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="17.1328125" customWidth="1"/>
+    <col min="5" max="5" width="23.06640625" customWidth="1"/>
+    <col min="6" max="6" width="16.53125" customWidth="1"/>
+    <col min="7" max="7" width="14.1328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>일자</v>
-      </c>
-      <c r="B1" t="str">
-        <v>분류</v>
-      </c>
-      <c r="C1" t="str">
-        <v>카테고리</v>
-      </c>
-      <c r="D1" t="str">
-        <v>금액</v>
-      </c>
-      <c r="E1" t="str">
-        <v>내용</v>
-      </c>
-      <c r="F1" t="str">
-        <v>결제수단</v>
-      </c>
-      <c r="G1" t="str">
-        <v>주체</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>수입</v>
-      </c>
-      <c r="C2" t="str">
-        <v>급여</v>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>3500000</v>
-      </c>
-      <c r="E2" t="str">
-        <v>남편 월급</v>
-      </c>
-      <c r="F2" t="str">
-        <v>계좌이체</v>
-      </c>
-      <c r="G2" t="str">
-        <v>남편</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-04-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>지출</v>
-      </c>
-      <c r="C3" t="str">
-        <v>마트/편의점</v>
+        <v>46300</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>65000</v>
-      </c>
-      <c r="E3" t="str">
-        <v>이마트 삼겹살 장보기</v>
-      </c>
-      <c r="F3" t="str">
-        <v>신용카드</v>
-      </c>
-      <c r="G3" t="str">
-        <v>아내</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="B4" t="str">
-        <v>지출</v>
-      </c>
-      <c r="C4" t="str">
-        <v>문화/여가</v>
+        <v>663300</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>32000</v>
-      </c>
-      <c r="E4" t="str">
-        <v>CGV 영화예매</v>
-      </c>
-      <c r="F4" t="str">
-        <v>신용카드</v>
-      </c>
-      <c r="G4" t="str">
-        <v>남편</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2026-04-07</v>
-      </c>
-      <c r="B5" t="str">
-        <v>지출</v>
-      </c>
-      <c r="C5" t="str">
-        <v>통신</v>
+        <v>2333400</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>85000</v>
-      </c>
-      <c r="E5" t="str">
-        <v>휴대폰 요금</v>
-      </c>
-      <c r="F5" t="str">
-        <v>계좌이체</v>
-      </c>
-      <c r="G5" t="str">
-        <v>아내</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="B6" t="str">
-        <v>지출</v>
-      </c>
-      <c r="C6" t="str">
-        <v>쇼핑/미용</v>
+        <v>16260</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>125000</v>
-      </c>
-      <c r="E6" t="str">
-        <v>봄맞이 자켓</v>
-      </c>
-      <c r="F6" t="str">
-        <v>신용카드</v>
-      </c>
-      <c r="G6" t="str">
-        <v>아내</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="B7" t="str">
-        <v>수입</v>
-      </c>
-      <c r="C7" t="str">
-        <v>부수입</v>
+        <v>16700</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>150000</v>
-      </c>
-      <c r="E7" t="str">
-        <v>안 쓰는 캠핑용품 당근 판매</v>
-      </c>
-      <c r="F7" t="str">
-        <v>현금</v>
-      </c>
-      <c r="G7" t="str">
-        <v>아내</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="B8" t="str">
-        <v>지출</v>
-      </c>
-      <c r="C8" t="str">
-        <v>외식</v>
+        <v>4500</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>12000</v>
-      </c>
-      <c r="E8" t="str">
-        <v>점심(국밥)</v>
-      </c>
-      <c r="F8" t="str">
-        <v>체크카드</v>
-      </c>
-      <c r="G8" t="str">
-        <v>남편</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>2026-04-25</v>
-      </c>
-      <c r="B9" t="str">
-        <v>지출</v>
-      </c>
-      <c r="C9" t="str">
-        <v>주거</v>
+        <v>1905</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>180000</v>
-      </c>
-      <c r="E9" t="str">
-        <v>아파트 관리비</v>
-      </c>
-      <c r="F9" t="str">
-        <v>계좌이체</v>
-      </c>
-      <c r="G9" t="str">
-        <v>남편</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="B10" t="str">
-        <v>지출</v>
-      </c>
-      <c r="C10" t="str">
-        <v>의료/건강</v>
+        <v>21900</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
       </c>
       <c r="D10">
-        <v>25000</v>
-      </c>
-      <c r="E10" t="str">
-        <v>내과/약국</v>
-      </c>
-      <c r="F10" t="str">
-        <v>신용카드</v>
-      </c>
-      <c r="G10" t="str">
-        <v>남편</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="B11" t="str">
-        <v>이체</v>
-      </c>
-      <c r="C11" t="str">
-        <v>저축</v>
+        <v>4000</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
       </c>
       <c r="D11">
-        <v>500000</v>
-      </c>
-      <c r="E11" t="str">
-        <v>정기적금</v>
-      </c>
-      <c r="F11" t="str">
-        <v>계좌이체</v>
-      </c>
-      <c r="G11" t="str">
-        <v>공용</v>
+        <v>196290</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <v>12950</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13">
+        <v>3700</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>10300</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15">
+        <v>6500</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16">
+        <v>4000</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17">
+        <v>10600</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18">
+        <v>47049</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19">
+        <v>150630</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20">
+        <v>73700</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>54855</v>
+      </c>
+      <c r="E21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22">
+        <v>3000</v>
+      </c>
+      <c r="E22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23">
+        <v>7600</v>
+      </c>
+      <c r="E23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24">
+        <v>7890</v>
+      </c>
+      <c r="E24" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25">
+        <v>13374</v>
+      </c>
+      <c r="E25" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26">
+        <v>10496</v>
+      </c>
+      <c r="E26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27">
+        <v>137095</v>
+      </c>
+      <c r="E27" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28">
+        <v>39710</v>
+      </c>
+      <c r="E28" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29">
+        <v>183990</v>
+      </c>
+      <c r="E29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>61900</v>
+      </c>
+      <c r="E30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>24900</v>
+      </c>
+      <c r="E31" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>13410</v>
+      </c>
+      <c r="E32" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33">
+        <v>27720</v>
+      </c>
+      <c r="E33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34">
+        <v>12600</v>
+      </c>
+      <c r="E34" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35">
+        <v>200000</v>
+      </c>
+      <c r="E35" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36">
+        <v>19800</v>
+      </c>
+      <c r="E36" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" t="s">
+        <v>9</v>
+      </c>
+      <c r="G36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37">
+        <v>10230</v>
+      </c>
+      <c r="E37" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" t="s">
+        <v>9</v>
+      </c>
+      <c r="G37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38">
+        <v>36220</v>
+      </c>
+      <c r="E38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39">
+        <v>18720</v>
+      </c>
+      <c r="E39" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40">
+        <v>44400</v>
+      </c>
+      <c r="E40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41">
+        <v>48430</v>
+      </c>
+      <c r="E41" t="s">
+        <v>47</v>
+      </c>
+      <c r="F41" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42">
+        <v>16700</v>
+      </c>
+      <c r="E42" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43">
+        <v>1500</v>
+      </c>
+      <c r="E43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F43" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44">
+        <v>14000</v>
+      </c>
+      <c r="E44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45">
+        <v>4650</v>
+      </c>
+      <c r="E45" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46">
+        <v>350</v>
+      </c>
+      <c r="E46" t="s">
+        <v>51</v>
+      </c>
+      <c r="F46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47">
+        <v>1650</v>
+      </c>
+      <c r="E47" t="s">
+        <v>52</v>
+      </c>
+      <c r="F47" t="s">
+        <v>9</v>
+      </c>
+      <c r="G47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48">
+        <v>1500</v>
+      </c>
+      <c r="E48" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" t="s">
+        <v>9</v>
+      </c>
+      <c r="G48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49">
+        <v>1650</v>
+      </c>
+      <c r="E49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50">
+        <v>5000</v>
+      </c>
+      <c r="E50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" t="s">
+        <v>9</v>
+      </c>
+      <c r="G50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51">
+        <v>12276</v>
+      </c>
+      <c r="E51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G51" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52">
+        <v>11733</v>
+      </c>
+      <c r="E52" t="s">
+        <v>58</v>
+      </c>
+      <c r="F52" t="s">
+        <v>9</v>
+      </c>
+      <c r="G52" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>